--- a/forms/trg/Formulir_TRG_fisher-g.xlsx
+++ b/forms/trg/Formulir_TRG_fisher-g.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B23)</f>
+        <f>COUNTA(Anggota!B5:B24)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F23)</f>
+        <f>COUNTA(Anggota!F5:F24)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,23 +925,31 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Marina Hasan</t>
+          <t>Prof. Dr. Ir. Hilal Anshary, M.Sc</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="12" t="n"/>
-      <c r="E5" s="11" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>xx</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>6507936913</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -954,12 +962,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Sriwulan</t>
+          <t>Marina Hasan</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D6" s="12" t="n"/>
@@ -983,12 +991,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dian Novita Sari</t>
+          <t>Sriwulan</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D7" s="12" t="n"/>
@@ -1012,12 +1020,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Gunarto Latama</t>
+          <t>Dian Novita Sari</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D8" s="12" t="n"/>
@@ -1041,19 +1049,15 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Ika</t>
+          <t>Gunarto Latama</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n"/>
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
@@ -1074,15 +1078,19 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Mutiyah Amalia Rachmat</t>
+          <t>Ika</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E10" s="11" t="n"/>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
@@ -1103,20 +1111,16 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Buana Basir</t>
+          <t>Mutiyah Amalia Rachmat</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D11" s="12" t="n"/>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>GGERG Team</t>
-        </is>
-      </c>
+      <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
@@ -1134,10 +1138,22 @@
       <c r="A12" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Buana Basir</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D12" s="12" t="n"/>
-      <c r="E12" s="11" t="n"/>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>GGERG Team</t>
+        </is>
+      </c>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
@@ -1145,7 +1161,11 @@
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1334,15 +1354,32 @@
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="12" t="n"/>
     </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
